--- a/docs/downloads/13082026Tduh Developer Project Sales Status 13.xlsx
+++ b/docs/downloads/13082026Tduh Developer Project Sales Status 13.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AW17"/>
+  <dimension ref="A2:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -537,6 +537,9 @@
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
     <col width="9" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="50" max="50"/>
+    <col width="9" customWidth="1" min="51" max="51"/>
+    <col width="9" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -594,8 +597,11 @@
       <c r="AR3" s="3" t="n">
         <v>46234</v>
       </c>
-      <c r="AU3" s="4" t="n">
+      <c r="AU3" s="3" t="n">
         <v>46241</v>
+      </c>
+      <c r="AX3" s="4" t="n">
+        <v>46248</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -831,17 +837,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="AU4" s="6" t="inlineStr">
+      <c r="AU4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="AV4" s="6" t="inlineStr">
+      <c r="AV4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AW4" s="6" t="inlineStr">
+      <c r="AW4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AX4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="AY4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AZ4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -910,9 +931,17 @@
       <c r="AR5" s="9" t="n"/>
       <c r="AS5" s="9" t="n"/>
       <c r="AT5" s="10" t="n"/>
-      <c r="AU5" s="11" t="n"/>
-      <c r="AV5" s="11" t="n"/>
-      <c r="AW5" s="12" t="n"/>
+      <c r="AU5" s="9" t="n"/>
+      <c r="AV5" s="9" t="n"/>
+      <c r="AW5" s="10" t="n"/>
+      <c r="AX5" s="11" t="n"/>
+      <c r="AY5" s="11" t="n">
+        <v>177</v>
+      </c>
+      <c r="AZ5" s="12">
+        <f>AY5/$E$5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1086,15 +1115,26 @@
         <f>AS6/$E$6</f>
         <v/>
       </c>
-      <c r="AU6" s="11">
+      <c r="AU6" s="9">
         <f>AV6-AS6</f>
         <v/>
       </c>
-      <c r="AV6" s="11" t="n">
+      <c r="AV6" s="9" t="n">
         <v>319</v>
       </c>
-      <c r="AW6" s="12">
+      <c r="AW6" s="10">
         <f>AV6/$E$6</f>
+        <v/>
+      </c>
+      <c r="AX6" s="11">
+        <f>AY6-AV6</f>
+        <v/>
+      </c>
+      <c r="AY6" s="11" t="n">
+        <v>334</v>
+      </c>
+      <c r="AZ6" s="12">
+        <f>AY6/$E$6</f>
         <v/>
       </c>
     </row>
@@ -1271,15 +1311,26 @@
         <f>AS7/$E$7</f>
         <v/>
       </c>
-      <c r="AU7" s="11">
+      <c r="AU7" s="9">
         <f>AV7-AS7</f>
         <v/>
       </c>
-      <c r="AV7" s="11" t="n">
+      <c r="AV7" s="9" t="n">
         <v>112</v>
       </c>
-      <c r="AW7" s="12">
+      <c r="AW7" s="10">
         <f>AV7/$E$7</f>
+        <v/>
+      </c>
+      <c r="AX7" s="11">
+        <f>AY7-AV7</f>
+        <v/>
+      </c>
+      <c r="AY7" s="11" t="n">
+        <v>119</v>
+      </c>
+      <c r="AZ7" s="12">
+        <f>AY7/$E$7</f>
         <v/>
       </c>
     </row>
@@ -1455,15 +1506,26 @@
         <f>AS8/$E$8</f>
         <v/>
       </c>
-      <c r="AU8" s="11">
+      <c r="AU8" s="9">
         <f>AV8-AS8</f>
         <v/>
       </c>
-      <c r="AV8" s="11" t="n">
+      <c r="AV8" s="9" t="n">
         <v>985</v>
       </c>
-      <c r="AW8" s="12">
+      <c r="AW8" s="10">
         <f>AV8/$E$8</f>
+        <v/>
+      </c>
+      <c r="AX8" s="11">
+        <f>AY8-AV8</f>
+        <v/>
+      </c>
+      <c r="AY8" s="11" t="n">
+        <v>996</v>
+      </c>
+      <c r="AZ8" s="12">
+        <f>AY8/$E$8</f>
         <v/>
       </c>
     </row>
@@ -1640,15 +1702,26 @@
         <f>AS9/$E$9</f>
         <v/>
       </c>
-      <c r="AU9" s="11">
+      <c r="AU9" s="9">
         <f>AV9-AS9</f>
         <v/>
       </c>
-      <c r="AV9" s="11" t="n">
+      <c r="AV9" s="9" t="n">
         <v>1119</v>
       </c>
-      <c r="AW9" s="12">
+      <c r="AW9" s="10">
         <f>AV9/$E$9</f>
+        <v/>
+      </c>
+      <c r="AX9" s="11">
+        <f>AY9-AV9</f>
+        <v/>
+      </c>
+      <c r="AY9" s="11" t="n">
+        <v>1125</v>
+      </c>
+      <c r="AZ9" s="12">
+        <f>AY9/$E$9</f>
         <v/>
       </c>
     </row>
@@ -1825,15 +1898,26 @@
         <f>AS10/$E$10</f>
         <v/>
       </c>
-      <c r="AU10" s="11">
+      <c r="AU10" s="9">
         <f>AV10-AS10</f>
         <v/>
       </c>
-      <c r="AV10" s="11" t="n">
+      <c r="AV10" s="9" t="n">
         <v>491</v>
       </c>
-      <c r="AW10" s="12">
+      <c r="AW10" s="10">
         <f>AV10/$E$10</f>
+        <v/>
+      </c>
+      <c r="AX10" s="11">
+        <f>AY10-AV10</f>
+        <v/>
+      </c>
+      <c r="AY10" s="11" t="n">
+        <v>499</v>
+      </c>
+      <c r="AZ10" s="12">
+        <f>AY10/$E$10</f>
         <v/>
       </c>
     </row>
@@ -2009,15 +2093,26 @@
         <f>AS11/$E$11</f>
         <v/>
       </c>
-      <c r="AU11" s="11">
+      <c r="AU11" s="9">
         <f>AV11-AS11</f>
         <v/>
       </c>
-      <c r="AV11" s="11" t="n">
+      <c r="AV11" s="9" t="n">
         <v>465</v>
       </c>
-      <c r="AW11" s="12">
+      <c r="AW11" s="10">
         <f>AV11/$E$11</f>
+        <v/>
+      </c>
+      <c r="AX11" s="11">
+        <f>AY11-AV11</f>
+        <v/>
+      </c>
+      <c r="AY11" s="11" t="n">
+        <v>467</v>
+      </c>
+      <c r="AZ11" s="12">
+        <f>AY11/$E$11</f>
         <v/>
       </c>
     </row>
@@ -2193,15 +2288,26 @@
         <f>AS12/$E$12</f>
         <v/>
       </c>
-      <c r="AU12" s="11">
+      <c r="AU12" s="9">
         <f>AV12-AS12</f>
         <v/>
       </c>
-      <c r="AV12" s="11" t="n">
+      <c r="AV12" s="9" t="n">
         <v>235</v>
       </c>
-      <c r="AW12" s="12">
+      <c r="AW12" s="10">
         <f>AV12/$E$12</f>
+        <v/>
+      </c>
+      <c r="AX12" s="11">
+        <f>AY12-AV12</f>
+        <v/>
+      </c>
+      <c r="AY12" s="11" t="n">
+        <v>236</v>
+      </c>
+      <c r="AZ12" s="12">
+        <f>AY12/$E$12</f>
         <v/>
       </c>
     </row>
@@ -2378,15 +2484,26 @@
         <f>AS13/$E$13</f>
         <v/>
       </c>
-      <c r="AU13" s="11">
+      <c r="AU13" s="9">
         <f>AV13-AS13</f>
         <v/>
       </c>
-      <c r="AV13" s="11" t="n">
+      <c r="AV13" s="9" t="n">
         <v>608</v>
       </c>
-      <c r="AW13" s="12">
+      <c r="AW13" s="10">
         <f>AV13/$E$13</f>
+        <v/>
+      </c>
+      <c r="AX13" s="11">
+        <f>AY13-AV13</f>
+        <v/>
+      </c>
+      <c r="AY13" s="11" t="n">
+        <v>618</v>
+      </c>
+      <c r="AZ13" s="12">
+        <f>AY13/$E$13</f>
         <v/>
       </c>
     </row>
@@ -2562,15 +2679,26 @@
         <f>AS14/$E$14</f>
         <v/>
       </c>
-      <c r="AU14" s="11">
+      <c r="AU14" s="9">
         <f>AV14-AS14</f>
         <v/>
       </c>
-      <c r="AV14" s="11" t="n">
+      <c r="AV14" s="9" t="n">
         <v>1139</v>
       </c>
-      <c r="AW14" s="12">
+      <c r="AW14" s="10">
         <f>AV14/$E$14</f>
+        <v/>
+      </c>
+      <c r="AX14" s="11">
+        <f>AY14-AV14</f>
+        <v/>
+      </c>
+      <c r="AY14" s="11" t="n">
+        <v>1142</v>
+      </c>
+      <c r="AZ14" s="12">
+        <f>AY14/$E$14</f>
         <v/>
       </c>
     </row>
@@ -2746,15 +2874,26 @@
         <f>AS15/$E$15</f>
         <v/>
       </c>
-      <c r="AU15" s="11">
+      <c r="AU15" s="9">
         <f>AV15-AS15</f>
         <v/>
       </c>
-      <c r="AV15" s="11" t="n">
+      <c r="AV15" s="9" t="n">
         <v>124</v>
       </c>
-      <c r="AW15" s="12">
+      <c r="AW15" s="10">
         <f>AV15/$E$15</f>
+        <v/>
+      </c>
+      <c r="AX15" s="11">
+        <f>AY15-AV15</f>
+        <v/>
+      </c>
+      <c r="AY15" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="AZ15" s="12">
+        <f>AY15/$E$15</f>
         <v/>
       </c>
     </row>
@@ -2866,15 +3005,26 @@
         <f>AS16/$E$16</f>
         <v/>
       </c>
-      <c r="AU16" s="11">
+      <c r="AU16" s="9">
         <f>AV16-AS16</f>
         <v/>
       </c>
-      <c r="AV16" s="11" t="n">
+      <c r="AV16" s="9" t="n">
         <v>659</v>
       </c>
-      <c r="AW16" s="12">
+      <c r="AW16" s="10">
         <f>AV16/$E$16</f>
+        <v/>
+      </c>
+      <c r="AX16" s="11">
+        <f>AY16-AV16</f>
+        <v/>
+      </c>
+      <c r="AY16" s="11" t="n">
+        <v>659</v>
+      </c>
+      <c r="AZ16" s="12">
+        <f>AY16/$E$16</f>
         <v/>
       </c>
     </row>
@@ -2937,12 +3087,15 @@
       <c r="AR17" s="9" t="n"/>
       <c r="AS17" s="9" t="n"/>
       <c r="AT17" s="10" t="n"/>
-      <c r="AU17" s="11" t="n"/>
-      <c r="AV17" s="11" t="n"/>
-      <c r="AW17" s="12" t="n"/>
+      <c r="AU17" s="9" t="n"/>
+      <c r="AV17" s="9" t="n"/>
+      <c r="AW17" s="10" t="n"/>
+      <c r="AX17" s="11" t="n"/>
+      <c r="AY17" s="11" t="n"/>
+      <c r="AZ17" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="AU3:AW3"/>
     <mergeCell ref="W3:Y3"/>
@@ -2951,6 +3104,7 @@
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="AC3:AE3"/>
     <mergeCell ref="AF3:AH3"/>
+    <mergeCell ref="AX3:AZ3"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="Z3:AB3"/>
